--- a/001.normalizacion.3FN.xlsx
+++ b/001.normalizacion.3FN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YE\Desktop\bootcampduckdb\contenido.curso\003.normalizacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YE\Desktop\Normalizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B86ED50-B8B8-4245-8394-EDA32ED36F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B513A770-E607-44CB-87BE-1B25960AF482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="230">
   <si>
     <t>Carivoros</t>
   </si>
@@ -776,6 +776,9 @@
   </si>
   <si>
     <t>Todos los atributos son atómicos, significa que el atributo no se puede dividir en partes más pequeñas o significativas. Es indivisible, lo que implica que el valor almacenado es una única unidad de información</t>
+  </si>
+  <si>
+    <t>REGLAS DE LA TERCERA FORMA NORMAL</t>
   </si>
 </sst>
 </file>
@@ -1129,6 +1132,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1156,6 +1168,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1170,12 +1188,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1197,15 +1209,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1667,126 +1670,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1">
-      <c r="A1" s="41"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
+      <c r="A1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
     </row>
     <row r="16" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
     </row>
     <row r="17" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
     </row>
     <row r="18" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
     </row>
     <row r="19" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
     </row>
     <row r="20" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
     </row>
     <row r="22" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
     </row>
     <row r="23" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
     </row>
     <row r="24" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
     </row>
     <row r="25" spans="1:3" s="23" customFormat="1">
       <c r="A25" s="14" t="s">
@@ -1816,42 +1819,42 @@
       </c>
     </row>
     <row r="28" spans="1:3" s="23" customFormat="1">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="42" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="47" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="23" customFormat="1">
-      <c r="A29" s="39"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C29" s="44"/>
+      <c r="C29" s="47"/>
     </row>
     <row r="30" spans="1:3" s="23" customFormat="1">
-      <c r="A30" s="39"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="47"/>
     </row>
     <row r="31" spans="1:3" s="23" customFormat="1">
-      <c r="A31" s="39"/>
+      <c r="A31" s="42"/>
       <c r="B31" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="47"/>
     </row>
     <row r="32" spans="1:3" s="1" customFormat="1">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="47" t="s">
         <v>1</v>
       </c>
       <c r="C32" s="37" t="s">
@@ -1859,22 +1862,22 @@
       </c>
     </row>
     <row r="33" spans="1:3" s="1" customFormat="1">
-      <c r="A33" s="39"/>
-      <c r="B33" s="44"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="47"/>
       <c r="C33" s="37" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:3" s="1" customFormat="1">
-      <c r="A34" s="39"/>
-      <c r="B34" s="44"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="47"/>
       <c r="C34" s="37" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:3" s="1" customFormat="1" ht="27.6">
-      <c r="A35" s="39"/>
-      <c r="B35" s="44" t="s">
+      <c r="A35" s="42"/>
+      <c r="B35" s="47" t="s">
         <v>222</v>
       </c>
       <c r="C35" s="37" t="s">
@@ -1882,22 +1885,22 @@
       </c>
     </row>
     <row r="36" spans="1:3" s="1" customFormat="1">
-      <c r="A36" s="39"/>
-      <c r="B36" s="44"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="47"/>
       <c r="C36" s="37" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:3" s="1" customFormat="1" ht="27.6">
-      <c r="A37" s="39"/>
-      <c r="B37" s="44"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="47"/>
       <c r="C37" s="37" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:3" s="1" customFormat="1" ht="27.6">
-      <c r="A38" s="39"/>
-      <c r="B38" s="44" t="s">
+      <c r="A38" s="42"/>
+      <c r="B38" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C38" s="37" t="s">
@@ -1905,22 +1908,22 @@
       </c>
     </row>
     <row r="39" spans="1:3" s="1" customFormat="1">
-      <c r="A39" s="39"/>
-      <c r="B39" s="44"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="47"/>
       <c r="C39" s="37" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="1" customFormat="1" ht="27.6">
-      <c r="A40" s="39"/>
-      <c r="B40" s="44"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="47"/>
       <c r="C40" s="37" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="1" customFormat="1">
-      <c r="A41" s="39"/>
-      <c r="B41" s="44" t="s">
+      <c r="A41" s="42"/>
+      <c r="B41" s="47" t="s">
         <v>223</v>
       </c>
       <c r="C41" s="37" t="s">
@@ -1928,162 +1931,162 @@
       </c>
     </row>
     <row r="42" spans="1:3" s="1" customFormat="1">
-      <c r="A42" s="39"/>
-      <c r="B42" s="44"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="47"/>
       <c r="C42" s="37" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:3" s="1" customFormat="1">
-      <c r="A43" s="39"/>
-      <c r="B43" s="44"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="47"/>
       <c r="C43" s="37" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:3" s="23" customFormat="1">
-      <c r="A44" s="39" t="s">
+      <c r="A44" s="42" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="44" t="s">
+      <c r="C44" s="47" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:3" s="23" customFormat="1">
-      <c r="A45" s="39"/>
+      <c r="A45" s="42"/>
       <c r="B45" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="44"/>
+      <c r="C45" s="47"/>
     </row>
     <row r="46" spans="1:3" s="23" customFormat="1">
-      <c r="A46" s="39"/>
+      <c r="A46" s="42"/>
       <c r="B46" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="44"/>
+      <c r="C46" s="47"/>
     </row>
     <row r="47" spans="1:3" s="18" customFormat="1">
-      <c r="A47" s="39" t="s">
+      <c r="A47" s="42" t="s">
         <v>8</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="45" t="s">
+      <c r="C47" s="48" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:3" s="18" customFormat="1">
-      <c r="A48" s="39"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="45"/>
+      <c r="C48" s="48"/>
     </row>
     <row r="49" spans="1:3" s="18" customFormat="1">
-      <c r="A49" s="39"/>
+      <c r="A49" s="42"/>
       <c r="B49" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C49" s="45"/>
+      <c r="C49" s="48"/>
     </row>
     <row r="50" spans="1:3" s="18" customFormat="1">
-      <c r="A50" s="39"/>
+      <c r="A50" s="42"/>
       <c r="B50" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="45"/>
+      <c r="C50" s="48"/>
     </row>
     <row r="51" spans="1:3" s="18" customFormat="1">
-      <c r="A51" s="39"/>
+      <c r="A51" s="42"/>
       <c r="B51" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="45"/>
+      <c r="C51" s="48"/>
     </row>
     <row r="52" spans="1:3" s="18" customFormat="1">
-      <c r="A52" s="39"/>
+      <c r="A52" s="42"/>
       <c r="B52" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="45"/>
+      <c r="C52" s="48"/>
     </row>
     <row r="53" spans="1:3" s="18" customFormat="1">
-      <c r="A53" s="39"/>
+      <c r="A53" s="42"/>
       <c r="B53" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="45"/>
+      <c r="C53" s="48"/>
     </row>
     <row r="54" spans="1:3" s="18" customFormat="1">
-      <c r="A54" s="39"/>
+      <c r="A54" s="42"/>
       <c r="B54" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="45"/>
+      <c r="C54" s="48"/>
     </row>
     <row r="55" spans="1:3" s="18" customFormat="1">
-      <c r="A55" s="39"/>
+      <c r="A55" s="42"/>
       <c r="B55" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="45"/>
+      <c r="C55" s="48"/>
     </row>
     <row r="56" spans="1:3" s="18" customFormat="1">
-      <c r="A56" s="39"/>
+      <c r="A56" s="42"/>
       <c r="B56" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="45"/>
+      <c r="C56" s="48"/>
     </row>
     <row r="57" spans="1:3" s="23" customFormat="1">
-      <c r="A57" s="39" t="s">
+      <c r="A57" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B57" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C57" s="44" t="s">
+      <c r="C57" s="47" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="23" customFormat="1">
-      <c r="A58" s="39"/>
+      <c r="A58" s="42"/>
       <c r="B58" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="44"/>
+      <c r="C58" s="47"/>
     </row>
     <row r="59" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A59" s="42" t="s">
+      <c r="A59" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="45"/>
     </row>
     <row r="60" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A60" s="43"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="43"/>
+      <c r="A60" s="46"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
     </row>
     <row r="61" spans="1:3" s="38" customFormat="1" ht="15" customHeight="1">
-      <c r="A61" s="43"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="43"/>
+      <c r="A61" s="46"/>
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
     </row>
     <row r="62" spans="1:3" s="38" customFormat="1" ht="20.399999999999999">
-      <c r="A62" s="43"/>
-      <c r="B62" s="43"/>
-      <c r="C62" s="43"/>
+      <c r="A62" s="46"/>
+      <c r="B62" s="46"/>
+      <c r="C62" s="46"/>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1">
-      <c r="A63" s="43"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
+      <c r="A63" s="46"/>
+      <c r="B63" s="46"/>
+      <c r="C63" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2127,16 +2130,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
@@ -2994,15 +2997,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="3" t="s">
@@ -3111,13 +3114,13 @@
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="48"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="55"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="1"/>
@@ -3127,15 +3130,15 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="1"/>
@@ -3151,13 +3154,13 @@
       <c r="B8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="1"/>
@@ -3173,13 +3176,13 @@
       <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="1"/>
@@ -3195,13 +3198,13 @@
       <c r="B10" s="11">
         <v>2</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
@@ -3220,13 +3223,13 @@
       <c r="B11" s="11">
         <v>3</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
@@ -3239,46 +3242,46 @@
       <c r="B12" s="11">
         <v>4</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="14" t="s">
@@ -8918,16 +8921,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A13:K13"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8957,44 +8960,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
     </row>
     <row r="2" spans="1:17" ht="27.6">
       <c r="A2" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="41" t="s">
         <v>95</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="41" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="14" t="s">
@@ -9003,10 +9006,10 @@
       <c r="J2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="63" t="s">
+      <c r="K2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="63" t="s">
+      <c r="L2" s="40" t="s">
         <v>9</v>
       </c>
     </row>
@@ -9170,13 +9173,13 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="48"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="50"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="55"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="1"/>
@@ -9186,20 +9189,20 @@
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
       <c r="M8" s="1"/>
       <c r="N8" s="17"/>
       <c r="O8" s="1"/>
@@ -9213,18 +9216,18 @@
       <c r="B9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
       <c r="M9" s="1"/>
       <c r="N9" s="17"/>
       <c r="O9" s="1"/>
@@ -9238,18 +9241,18 @@
       <c r="B10" s="11">
         <v>1</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="52"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
       <c r="M10" s="1"/>
       <c r="N10" s="17"/>
       <c r="O10" s="1"/>
@@ -9263,18 +9266,18 @@
       <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
       <c r="M11" s="1"/>
       <c r="N11" s="17"/>
       <c r="O11" s="1"/>
@@ -9282,24 +9285,24 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" ht="42" customHeight="1">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="39" t="s">
         <v>207</v>
       </c>
       <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
       <c r="M12" s="1"/>
       <c r="N12" s="17"/>
       <c r="O12" s="1"/>
@@ -9313,47 +9316,47 @@
       <c r="B13" s="11">
         <v>4</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="51"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="L15" s="55" t="s">
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="64"/>
+      <c r="L15" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="M15" s="55"/>
+      <c r="M15" s="58"/>
       <c r="N15"/>
     </row>
     <row r="16" spans="1:17">
@@ -9749,10 +9752,10 @@
       <c r="H28" s="15">
         <v>2</v>
       </c>
-      <c r="L28" s="57" t="s">
+      <c r="L28" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="M28" s="59"/>
+      <c r="M28" s="62"/>
       <c r="N28"/>
     </row>
     <row r="29" spans="1:14">
@@ -9923,11 +9926,11 @@
       <c r="H34" s="15">
         <v>1</v>
       </c>
-      <c r="L34" s="57" t="s">
+      <c r="L34" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="M34" s="58"/>
-      <c r="N34" s="59"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="62"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="15">
@@ -10380,15 +10383,15 @@
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
-      <c r="H49" s="55" t="s">
+      <c r="H49" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
-      <c r="L49" s="55" t="s">
+      <c r="I49" s="58"/>
+      <c r="J49" s="58"/>
+      <c r="L49" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="M49" s="55"/>
+      <c r="M49" s="58"/>
     </row>
     <row r="50" spans="2:13">
       <c r="B50"/>
@@ -12822,6 +12825,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="H8:L13"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="A7:G7"/>
@@ -12830,14 +12841,6 @@
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="H8:L13"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="A15:H15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12866,15 +12869,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="A1" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
       <c r="K1" s="17"/>
       <c r="L1" s="17"/>
       <c r="O1" s="1"/>
@@ -12888,13 +12891,13 @@
       <c r="B2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
       <c r="K2" s="17"/>
       <c r="L2" s="1"/>
       <c r="O2" s="1"/>
@@ -12908,13 +12911,13 @@
       <c r="B3" s="11">
         <v>1</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
       <c r="K3" s="17"/>
       <c r="L3" s="1"/>
       <c r="O3" s="1"/>
@@ -12928,13 +12931,13 @@
       <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="52" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
@@ -12947,34 +12950,34 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="55" t="s">
+      <c r="A5" s="56"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="M5" s="55"/>
+      <c r="M5" s="58"/>
       <c r="N5" s="17"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
       <c r="L6" s="15" t="s">
         <v>211</v>
       </c>
@@ -13345,10 +13348,10 @@
       <c r="H18" s="15">
         <v>2</v>
       </c>
-      <c r="L18" s="57" t="s">
+      <c r="L18" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="59"/>
+      <c r="M18" s="62"/>
       <c r="N18"/>
     </row>
     <row r="19" spans="1:14">
@@ -13517,11 +13520,11 @@
       <c r="H24" s="15">
         <v>2</v>
       </c>
-      <c r="L24" s="57" t="s">
+      <c r="L24" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="M24" s="58"/>
-      <c r="N24" s="59"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="62"/>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="15">
@@ -14018,25 +14021,25 @@
       <c r="M40" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="O40" s="55" t="s">
+      <c r="O40" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
     </row>
     <row r="41" spans="1:17" s="2" customFormat="1">
-      <c r="A41" s="52"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="57" t="s">
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="I41" s="58"/>
-      <c r="J41" s="59"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="62"/>
       <c r="L41" s="26">
         <v>1</v>
       </c>
@@ -14054,13 +14057,13 @@
       </c>
     </row>
     <row r="42" spans="1:17" s="2" customFormat="1">
-      <c r="A42" s="52"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
       <c r="H42" s="15" t="s">
         <v>209</v>
       </c>
@@ -14087,13 +14090,13 @@
       </c>
     </row>
     <row r="43" spans="1:17" s="2" customFormat="1">
-      <c r="A43" s="52"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
       <c r="H43" s="27">
         <v>1</v>
       </c>
@@ -14120,13 +14123,13 @@
       </c>
     </row>
     <row r="44" spans="1:17" s="2" customFormat="1">
-      <c r="A44" s="52"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
       <c r="H44" s="27">
         <v>2</v>
       </c>
@@ -14153,13 +14156,13 @@
       </c>
     </row>
     <row r="45" spans="1:17" s="2" customFormat="1">
-      <c r="A45" s="52"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
       <c r="H45" s="15">
         <v>3</v>
       </c>
@@ -14186,13 +14189,13 @@
       </c>
     </row>
     <row r="46" spans="1:17" s="2" customFormat="1">
-      <c r="A46" s="52"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
       <c r="H46" s="15">
         <v>4</v>
       </c>
@@ -14219,13 +14222,13 @@
       </c>
     </row>
     <row r="47" spans="1:17" s="2" customFormat="1">
-      <c r="A47" s="52"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
       <c r="H47" s="15">
         <v>5</v>
       </c>
@@ -14252,13 +14255,13 @@
       </c>
     </row>
     <row r="48" spans="1:17" s="2" customFormat="1">
-      <c r="A48" s="52"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
       <c r="H48" s="15">
         <v>6</v>
       </c>
@@ -14285,13 +14288,13 @@
       </c>
     </row>
     <row r="49" spans="1:17" s="2" customFormat="1">
-      <c r="A49" s="52"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
       <c r="H49" s="15">
         <v>7</v>
       </c>
@@ -14318,13 +14321,13 @@
       </c>
     </row>
     <row r="50" spans="1:17" s="2" customFormat="1">
-      <c r="A50" s="52"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
       <c r="H50" s="15">
         <v>8</v>
       </c>
@@ -14351,13 +14354,13 @@
       </c>
     </row>
     <row r="51" spans="1:17" s="2" customFormat="1">
-      <c r="A51" s="52"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
       <c r="H51" s="15">
         <v>9</v>
       </c>
@@ -14384,13 +14387,13 @@
       </c>
     </row>
     <row r="52" spans="1:17" s="2" customFormat="1">
-      <c r="A52" s="52"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
       <c r="H52" s="15">
         <v>10</v>
       </c>
@@ -14417,13 +14420,13 @@
       </c>
     </row>
     <row r="53" spans="1:17" s="2" customFormat="1">
-      <c r="A53" s="52"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
       <c r="H53" s="15">
         <v>11</v>
       </c>
@@ -14450,13 +14453,13 @@
       </c>
     </row>
     <row r="54" spans="1:17" s="2" customFormat="1">
-      <c r="A54" s="52"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
+      <c r="A54" s="57"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
       <c r="H54" s="15">
         <v>12</v>
       </c>
@@ -14483,13 +14486,13 @@
       </c>
     </row>
     <row r="55" spans="1:17" s="2" customFormat="1">
-      <c r="A55" s="52"/>
-      <c r="B55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
+      <c r="A55" s="57"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55"/>
@@ -14510,13 +14513,13 @@
       </c>
     </row>
     <row r="56" spans="1:17" s="2" customFormat="1">
-      <c r="A56" s="52"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
+      <c r="A56" s="57"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
       <c r="H56"/>
       <c r="I56"/>
       <c r="J56"/>
@@ -14537,13 +14540,13 @@
       </c>
     </row>
     <row r="57" spans="1:17" s="2" customFormat="1">
-      <c r="A57" s="52"/>
-      <c r="B57" s="52"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="52"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="52"/>
+      <c r="A57" s="57"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
       <c r="H57"/>
       <c r="I57"/>
       <c r="J57"/>
@@ -14564,17 +14567,17 @@
       </c>
     </row>
     <row r="58" spans="1:17" s="2" customFormat="1">
-      <c r="A58" s="52"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="41" t="s">
+      <c r="A58" s="57"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="44" t="s">
         <v>217</v>
       </c>
-      <c r="I58" s="41"/>
+      <c r="I58" s="44"/>
       <c r="J58"/>
       <c r="L58" s="15">
         <v>7</v>
@@ -14593,13 +14596,13 @@
       </c>
     </row>
     <row r="59" spans="1:17" s="2" customFormat="1">
-      <c r="A59" s="52"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
+      <c r="A59" s="57"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
       <c r="H59" s="15" t="s">
         <v>210</v>
       </c>
@@ -14624,13 +14627,13 @@
       </c>
     </row>
     <row r="60" spans="1:17" s="2" customFormat="1">
-      <c r="A60" s="52"/>
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="52"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="52"/>
+      <c r="A60" s="57"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
       <c r="H60" s="15">
         <v>1</v>
       </c>
@@ -14655,13 +14658,13 @@
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1">
-      <c r="A61" s="52"/>
-      <c r="B61" s="52"/>
-      <c r="C61" s="52"/>
-      <c r="D61" s="52"/>
-      <c r="E61" s="52"/>
-      <c r="F61" s="52"/>
-      <c r="G61" s="52"/>
+      <c r="A61" s="57"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57"/>
       <c r="H61" s="15">
         <v>2</v>
       </c>
@@ -14686,13 +14689,13 @@
       </c>
     </row>
     <row r="62" spans="1:17" s="2" customFormat="1">
-      <c r="A62" s="52"/>
-      <c r="B62" s="52"/>
-      <c r="C62" s="52"/>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="52"/>
+      <c r="A62" s="57"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
       <c r="H62" s="15">
         <v>3</v>
       </c>
@@ -14717,13 +14720,13 @@
       </c>
     </row>
     <row r="63" spans="1:17" s="2" customFormat="1">
-      <c r="A63" s="52"/>
-      <c r="B63" s="52"/>
-      <c r="C63" s="52"/>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="52"/>
+      <c r="A63" s="57"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
       <c r="H63" s="15">
         <v>4</v>
       </c>
@@ -14748,13 +14751,13 @@
       </c>
     </row>
     <row r="64" spans="1:17" s="2" customFormat="1">
-      <c r="A64" s="52"/>
-      <c r="B64" s="52"/>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
+      <c r="A64" s="57"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
       <c r="H64"/>
       <c r="I64"/>
       <c r="J64"/>
@@ -14775,13 +14778,13 @@
       </c>
     </row>
     <row r="65" spans="1:17" s="2" customFormat="1">
-      <c r="A65" s="52"/>
-      <c r="B65" s="52"/>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
+      <c r="A65" s="57"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
       <c r="H65"/>
       <c r="I65"/>
       <c r="J65"/>
@@ -14802,13 +14805,13 @@
       </c>
     </row>
     <row r="66" spans="1:17" s="2" customFormat="1">
-      <c r="A66" s="52"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
+      <c r="A66" s="57"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
       <c r="H66"/>
       <c r="I66"/>
       <c r="J66"/>
@@ -14829,13 +14832,13 @@
       </c>
     </row>
     <row r="67" spans="1:17" s="2" customFormat="1">
-      <c r="A67" s="52"/>
-      <c r="B67" s="52"/>
-      <c r="C67" s="52"/>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="52"/>
+      <c r="A67" s="57"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
       <c r="H67"/>
       <c r="I67"/>
       <c r="J67"/>
@@ -14856,13 +14859,13 @@
       </c>
     </row>
     <row r="68" spans="1:17" s="2" customFormat="1">
-      <c r="A68" s="52"/>
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="52"/>
+      <c r="A68" s="57"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
       <c r="H68"/>
       <c r="I68"/>
       <c r="J68"/>
@@ -17250,6 +17253,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="O40:Q40"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A41:G68"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="L18:M18"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="H41:J41"/>
@@ -17257,12 +17266,6 @@
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="O40:Q40"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A41:G68"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="L18:M18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
